--- a/tests/testdata/excel/フォルダ/隠しフォルダ/隠しフォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/隠しフォルダ/隠しフォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3338EC5A-8A7A-4E64-9074-725BEEA93C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD89D76A-DC5F-4803-8C40-5B3C9A817CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{8255980F-67BC-4318-9BFE-9E2D1DE4A1C7}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{804FB91B-1AD9-4490-9F72-88DF4105F7B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2017466D-BC78-46A7-93DD-9C70E213FB13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BE752B-8A8D-4FB8-9B1F-21CE059CB70C}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/フォルダ/隠しフォルダ/隠しフォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/隠しフォルダ/隠しフォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD89D76A-DC5F-4803-8C40-5B3C9A817CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA177E25-9C93-4E64-9C9D-8A32C424B3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{804FB91B-1AD9-4490-9F72-88DF4105F7B2}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{1D79176D-4ABC-435C-AF5A-41F9B6EEBD1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BE752B-8A8D-4FB8-9B1F-21CE059CB70C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF0873CB-CC76-4CEF-8C44-0D259AB6BFEF}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
